--- a/Shablon/TDS2014B.xlsx
+++ b/Shablon/TDS2014B.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="333">
   <si>
     <t>Канал 1</t>
   </si>
@@ -846,51 +846,6 @@
     <t>ti1_5</t>
   </si>
   <si>
-    <t>ti2_1</t>
-  </si>
-  <si>
-    <t>ti2_2</t>
-  </si>
-  <si>
-    <t>ti2_3</t>
-  </si>
-  <si>
-    <t>ti2_4</t>
-  </si>
-  <si>
-    <t>ti2_5</t>
-  </si>
-  <si>
-    <t>ti3_1</t>
-  </si>
-  <si>
-    <t>ti3_2</t>
-  </si>
-  <si>
-    <t>ti3_3</t>
-  </si>
-  <si>
-    <t>ti3_4</t>
-  </si>
-  <si>
-    <t>ti3_5</t>
-  </si>
-  <si>
-    <t>ti4_1</t>
-  </si>
-  <si>
-    <t>ti4_2</t>
-  </si>
-  <si>
-    <t>ti4_3</t>
-  </si>
-  <si>
-    <t>ti4_4</t>
-  </si>
-  <si>
-    <t>ti4_5</t>
-  </si>
-  <si>
     <t>gti1_1</t>
   </si>
   <si>
@@ -904,51 +859,6 @@
   </si>
   <si>
     <t>gti1_5</t>
-  </si>
-  <si>
-    <t>gti2_1</t>
-  </si>
-  <si>
-    <t>gti2_2</t>
-  </si>
-  <si>
-    <t>gti2_3</t>
-  </si>
-  <si>
-    <t>gti2_4</t>
-  </si>
-  <si>
-    <t>gti2_5</t>
-  </si>
-  <si>
-    <t>gti3_1</t>
-  </si>
-  <si>
-    <t>gti3_2</t>
-  </si>
-  <si>
-    <t>gti3_3</t>
-  </si>
-  <si>
-    <t>gti3_4</t>
-  </si>
-  <si>
-    <t>gti3_5</t>
-  </si>
-  <si>
-    <t>gti4_1</t>
-  </si>
-  <si>
-    <t>gti4_2</t>
-  </si>
-  <si>
-    <t>gti4_3</t>
-  </si>
-  <si>
-    <t>gti4_4</t>
-  </si>
-  <si>
-    <t>gti4_5</t>
   </si>
   <si>
     <t>tr1_1</t>
@@ -1577,13 +1487,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1593,73 +1569,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1968,7 +1878,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2051,19 +1961,19 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="str">
-        <f>"Протокол поверки № 10/"&amp;C152&amp;"/"&amp;D10</f>
+      <c r="A7" s="71" t="str">
+        <f>"Протокол поверки № 10/"&amp;C137&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="30"/>
@@ -2078,11 +1988,11 @@
       <c r="J8" s="30"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
       <c r="D9" s="27" t="s">
         <v>83</v>
       </c>
@@ -2096,11 +2006,11 @@
       <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
       <c r="D10" s="36" t="s">
         <v>5</v>
       </c>
@@ -2112,11 +2022,11 @@
       <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
       <c r="D11" s="27"/>
       <c r="E11" s="28"/>
       <c r="F11" s="28"/>
@@ -2126,13 +2036,13 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
       <c r="D12" s="26" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="28"/>
@@ -2142,11 +2052,11 @@
       <c r="J12" s="29"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="36" t="s">
         <v>6</v>
       </c>
@@ -2158,11 +2068,11 @@
       <c r="J13" s="29"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
       <c r="D14" s="26" t="s">
         <v>89</v>
       </c>
@@ -2174,11 +2084,11 @@
       <c r="J14" s="29"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
       <c r="D15" s="27" t="s">
         <v>91</v>
       </c>
@@ -2216,113 +2126,113 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50" t="s">
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="51" t="s">
+      <c r="F18" s="46"/>
+      <c r="G18" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="51"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="1"/>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47" t="s">
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48" t="s">
+      <c r="F20" s="69"/>
+      <c r="G20" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="48"/>
+      <c r="H20" s="70"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47" t="s">
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="48" t="s">
+      <c r="F21" s="69"/>
+      <c r="G21" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="48"/>
+      <c r="H21" s="70"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47" t="s">
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="47"/>
-      <c r="G22" s="48" t="s">
+      <c r="F22" s="69"/>
+      <c r="G22" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="48"/>
+      <c r="H22" s="70"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="48" t="s">
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="48"/>
+      <c r="H23" s="70"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="48" t="s">
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="48"/>
+      <c r="H24" s="70"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -2338,7 +2248,7 @@
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -2362,7 +2272,7 @@
     </row>
     <row r="28" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2386,7 +2296,7 @@
     </row>
     <row r="30" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2410,7 +2320,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2449,94 +2359,94 @@
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="51" t="s">
+      <c r="A35" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="50" t="s">
+      <c r="B35" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50" t="s">
+      <c r="D35" s="46"/>
+      <c r="E35" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50" t="s">
+      <c r="F35" s="46"/>
+      <c r="G35" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50" t="s">
+      <c r="H35" s="46"/>
+      <c r="I35" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="J35" s="50"/>
+      <c r="J35" s="46"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="51"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="51"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="51"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
       <c r="G39" s="16" t="s">
         <v>2</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="50" t="s">
+      <c r="A40" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
@@ -2545,24 +2455,24 @@
       <c r="B41" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="52" t="s">
+      <c r="C41" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52" t="s">
+      <c r="D41" s="56"/>
+      <c r="E41" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="52"/>
+      <c r="F41" s="56"/>
       <c r="G41" s="11" t="s">
         <v>96</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I41" s="49">
+      <c r="I41" s="53">
         <v>4</v>
       </c>
-      <c r="J41" s="49"/>
+      <c r="J41" s="53"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
@@ -2571,22 +2481,22 @@
       <c r="B42" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52" t="s">
+      <c r="D42" s="56"/>
+      <c r="E42" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="F42" s="52"/>
+      <c r="F42" s="56"/>
       <c r="G42" s="11" t="s">
         <v>100</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
@@ -2595,24 +2505,24 @@
       <c r="B43" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="52" t="s">
+      <c r="C43" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52" t="s">
+      <c r="D43" s="56"/>
+      <c r="E43" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="52"/>
+      <c r="F43" s="56"/>
       <c r="G43" s="11" t="s">
         <v>104</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="I43" s="53" t="s">
+      <c r="I43" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="J43" s="53"/>
+      <c r="J43" s="64"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
@@ -2621,22 +2531,22 @@
       <c r="B44" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C44" s="52" t="s">
+      <c r="C44" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52" t="s">
+      <c r="D44" s="56"/>
+      <c r="E44" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="F44" s="52"/>
+      <c r="F44" s="56"/>
       <c r="G44" s="11" t="s">
         <v>108</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
@@ -2645,22 +2555,22 @@
       <c r="B45" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52" t="s">
+      <c r="D45" s="56"/>
+      <c r="E45" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="52"/>
+      <c r="F45" s="56"/>
       <c r="G45" s="11" t="s">
         <v>112</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
@@ -2669,22 +2579,22 @@
       <c r="B46" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52" t="s">
+      <c r="D46" s="56"/>
+      <c r="E46" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="52"/>
+      <c r="F46" s="56"/>
       <c r="G46" s="11" t="s">
         <v>116</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="I46" s="53"/>
-      <c r="J46" s="53"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="64"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
@@ -2693,22 +2603,22 @@
       <c r="B47" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52" t="s">
+      <c r="D47" s="56"/>
+      <c r="E47" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="52"/>
+      <c r="F47" s="56"/>
       <c r="G47" s="11" t="s">
         <v>120</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="64"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
@@ -2717,22 +2627,22 @@
       <c r="B48" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52" t="s">
+      <c r="D48" s="56"/>
+      <c r="E48" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="F48" s="52"/>
+      <c r="F48" s="56"/>
       <c r="G48" s="11" t="s">
         <v>124</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
+      <c r="I48" s="64"/>
+      <c r="J48" s="64"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
@@ -2741,22 +2651,22 @@
       <c r="B49" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52" t="s">
+      <c r="D49" s="56"/>
+      <c r="E49" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="F49" s="52"/>
+      <c r="F49" s="56"/>
       <c r="G49" s="11" t="s">
         <v>128</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
+      <c r="I49" s="64"/>
+      <c r="J49" s="64"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
@@ -2765,22 +2675,22 @@
       <c r="B50" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52" t="s">
+      <c r="D50" s="56"/>
+      <c r="E50" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="F50" s="52"/>
+      <c r="F50" s="56"/>
       <c r="G50" s="11" t="s">
         <v>132</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
+      <c r="I50" s="64"/>
+      <c r="J50" s="64"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
@@ -2789,22 +2699,22 @@
       <c r="B51" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52" t="s">
+      <c r="D51" s="56"/>
+      <c r="E51" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="F51" s="52"/>
+      <c r="F51" s="56"/>
       <c r="G51" s="11" t="s">
         <v>136</v>
       </c>
       <c r="H51" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
+      <c r="I51" s="64"/>
+      <c r="J51" s="64"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="22"/>
@@ -2831,94 +2741,94 @@
       <c r="J53" s="25"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="51" t="s">
+      <c r="A54" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="C54" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50" t="s">
+      <c r="D54" s="46"/>
+      <c r="E54" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="50"/>
-      <c r="G54" s="50" t="s">
+      <c r="F54" s="46"/>
+      <c r="G54" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="H54" s="50"/>
-      <c r="I54" s="50" t="s">
+      <c r="H54" s="46"/>
+      <c r="I54" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="J54" s="50"/>
+      <c r="J54" s="46"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55" s="51"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="50"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="50"/>
-      <c r="J55" s="50"/>
+      <c r="A55" s="57"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="51"/>
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="51"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="50"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="46"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="46"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="46"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" s="51"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
       <c r="G58" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="56" t="s">
+      <c r="A59" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="57"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
-      <c r="J59" s="57"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
@@ -2927,24 +2837,24 @@
       <c r="B60" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="52" t="s">
+      <c r="C60" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="D60" s="52"/>
-      <c r="E60" s="52" t="s">
+      <c r="D60" s="56"/>
+      <c r="E60" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="F60" s="52"/>
+      <c r="F60" s="56"/>
       <c r="G60" s="11" t="s">
         <v>140</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="I60" s="49">
+      <c r="I60" s="53">
         <v>4</v>
       </c>
-      <c r="J60" s="49"/>
+      <c r="J60" s="53"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
@@ -2953,22 +2863,22 @@
       <c r="B61" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="52" t="s">
+      <c r="C61" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="52"/>
-      <c r="E61" s="52" t="s">
+      <c r="D61" s="56"/>
+      <c r="E61" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="F61" s="52"/>
+      <c r="F61" s="56"/>
       <c r="G61" s="11" t="s">
         <v>144</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
@@ -2977,24 +2887,24 @@
       <c r="B62" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C62" s="52" t="s">
+      <c r="C62" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52" t="s">
+      <c r="D62" s="56"/>
+      <c r="E62" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="F62" s="52"/>
+      <c r="F62" s="56"/>
       <c r="G62" s="11" t="s">
         <v>148</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="I62" s="53" t="s">
+      <c r="I62" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="J62" s="53"/>
+      <c r="J62" s="64"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
@@ -3003,22 +2913,22 @@
       <c r="B63" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52" t="s">
+      <c r="D63" s="56"/>
+      <c r="E63" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="F63" s="52"/>
+      <c r="F63" s="56"/>
       <c r="G63" s="11" t="s">
         <v>152</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="I63" s="53"/>
-      <c r="J63" s="53"/>
+      <c r="I63" s="64"/>
+      <c r="J63" s="64"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
@@ -3027,22 +2937,22 @@
       <c r="B64" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52" t="s">
+      <c r="D64" s="56"/>
+      <c r="E64" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="F64" s="52"/>
+      <c r="F64" s="56"/>
       <c r="G64" s="11" t="s">
         <v>156</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="I64" s="53"/>
-      <c r="J64" s="53"/>
+      <c r="I64" s="64"/>
+      <c r="J64" s="64"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
@@ -3051,22 +2961,22 @@
       <c r="B65" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C65" s="52" t="s">
+      <c r="C65" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52" t="s">
+      <c r="D65" s="56"/>
+      <c r="E65" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="F65" s="52"/>
+      <c r="F65" s="56"/>
       <c r="G65" s="11" t="s">
         <v>160</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
+      <c r="I65" s="64"/>
+      <c r="J65" s="64"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
@@ -3075,22 +2985,22 @@
       <c r="B66" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="52" t="s">
+      <c r="C66" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52" t="s">
+      <c r="D66" s="56"/>
+      <c r="E66" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="F66" s="52"/>
+      <c r="F66" s="56"/>
       <c r="G66" s="11" t="s">
         <v>164</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
@@ -3099,22 +3009,22 @@
       <c r="B67" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C67" s="52" t="s">
+      <c r="C67" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52" t="s">
+      <c r="D67" s="56"/>
+      <c r="E67" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="F67" s="52"/>
+      <c r="F67" s="56"/>
       <c r="G67" s="11" t="s">
         <v>168</v>
       </c>
       <c r="H67" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="I67" s="53"/>
-      <c r="J67" s="53"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="64"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
@@ -3123,22 +3033,22 @@
       <c r="B68" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="52" t="s">
+      <c r="C68" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52" t="s">
+      <c r="D68" s="56"/>
+      <c r="E68" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="F68" s="52"/>
+      <c r="F68" s="56"/>
       <c r="G68" s="11" t="s">
         <v>172</v>
       </c>
       <c r="H68" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="I68" s="53"/>
-      <c r="J68" s="53"/>
+      <c r="I68" s="64"/>
+      <c r="J68" s="64"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
@@ -3147,22 +3057,22 @@
       <c r="B69" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C69" s="52" t="s">
+      <c r="C69" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52" t="s">
+      <c r="D69" s="56"/>
+      <c r="E69" s="56" t="s">
         <v>175</v>
       </c>
-      <c r="F69" s="52"/>
+      <c r="F69" s="56"/>
       <c r="G69" s="11" t="s">
         <v>176</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="I69" s="53"/>
-      <c r="J69" s="53"/>
+      <c r="I69" s="64"/>
+      <c r="J69" s="64"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
@@ -3171,36 +3081,36 @@
       <c r="B70" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C70" s="52" t="s">
+      <c r="C70" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52" t="s">
+      <c r="D70" s="56"/>
+      <c r="E70" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="F70" s="52"/>
+      <c r="F70" s="56"/>
       <c r="G70" s="11" t="s">
         <v>180</v>
       </c>
       <c r="H70" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="I70" s="53"/>
-      <c r="J70" s="53"/>
+      <c r="I70" s="64"/>
+      <c r="J70" s="64"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71" s="54" t="s">
+      <c r="A71" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="55"/>
-      <c r="C71" s="55"/>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="G71" s="55"/>
-      <c r="H71" s="55"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="66"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="66"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
@@ -3209,24 +3119,24 @@
       <c r="B72" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C72" s="52" t="s">
+      <c r="C72" s="56" t="s">
         <v>182</v>
       </c>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52" t="s">
+      <c r="D72" s="56"/>
+      <c r="E72" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="F72" s="52"/>
+      <c r="F72" s="56"/>
       <c r="G72" s="11" t="s">
         <v>184</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I72" s="49">
+      <c r="I72" s="53">
         <v>4</v>
       </c>
-      <c r="J72" s="49"/>
+      <c r="J72" s="53"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
@@ -3235,22 +3145,22 @@
       <c r="B73" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="52" t="s">
+      <c r="C73" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52" t="s">
+      <c r="D73" s="56"/>
+      <c r="E73" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="F73" s="52"/>
+      <c r="F73" s="56"/>
       <c r="G73" s="11" t="s">
         <v>188</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="I73" s="49"/>
-      <c r="J73" s="49"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
@@ -3259,24 +3169,24 @@
       <c r="B74" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="52" t="s">
+      <c r="C74" s="56" t="s">
         <v>190</v>
       </c>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52" t="s">
+      <c r="D74" s="56"/>
+      <c r="E74" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="F74" s="52"/>
+      <c r="F74" s="56"/>
       <c r="G74" s="11" t="s">
         <v>192</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="I74" s="53" t="s">
+      <c r="I74" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="J74" s="53"/>
+      <c r="J74" s="64"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
@@ -3285,22 +3195,22 @@
       <c r="B75" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="52" t="s">
+      <c r="C75" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52" t="s">
+      <c r="D75" s="56"/>
+      <c r="E75" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="F75" s="52"/>
+      <c r="F75" s="56"/>
       <c r="G75" s="11" t="s">
         <v>196</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
+      <c r="I75" s="64"/>
+      <c r="J75" s="64"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
@@ -3309,22 +3219,22 @@
       <c r="B76" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C76" s="52" t="s">
+      <c r="C76" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52" t="s">
+      <c r="D76" s="56"/>
+      <c r="E76" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="F76" s="52"/>
+      <c r="F76" s="56"/>
       <c r="G76" s="11" t="s">
         <v>200</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
+      <c r="I76" s="64"/>
+      <c r="J76" s="64"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
@@ -3333,22 +3243,22 @@
       <c r="B77" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="52" t="s">
+      <c r="C77" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52" t="s">
+      <c r="D77" s="56"/>
+      <c r="E77" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="F77" s="52"/>
+      <c r="F77" s="56"/>
       <c r="G77" s="11" t="s">
         <v>204</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="I77" s="53"/>
-      <c r="J77" s="53"/>
+      <c r="I77" s="64"/>
+      <c r="J77" s="64"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
@@ -3357,22 +3267,22 @@
       <c r="B78" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C78" s="52" t="s">
+      <c r="C78" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52" t="s">
+      <c r="D78" s="56"/>
+      <c r="E78" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="F78" s="52"/>
+      <c r="F78" s="56"/>
       <c r="G78" s="11" t="s">
         <v>208</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="I78" s="53"/>
-      <c r="J78" s="53"/>
+      <c r="I78" s="64"/>
+      <c r="J78" s="64"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
@@ -3381,22 +3291,22 @@
       <c r="B79" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C79" s="52" t="s">
+      <c r="C79" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52" t="s">
+      <c r="D79" s="56"/>
+      <c r="E79" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="F79" s="52"/>
+      <c r="F79" s="56"/>
       <c r="G79" s="11" t="s">
         <v>212</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
+      <c r="I79" s="64"/>
+      <c r="J79" s="64"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
@@ -3405,22 +3315,22 @@
       <c r="B80" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C80" s="52" t="s">
+      <c r="C80" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52" t="s">
+      <c r="D80" s="56"/>
+      <c r="E80" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="F80" s="52"/>
+      <c r="F80" s="56"/>
       <c r="G80" s="11" t="s">
         <v>216</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="I80" s="53"/>
-      <c r="J80" s="53"/>
+      <c r="I80" s="64"/>
+      <c r="J80" s="64"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
@@ -3429,22 +3339,22 @@
       <c r="B81" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="52" t="s">
+      <c r="C81" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52" t="s">
+      <c r="D81" s="56"/>
+      <c r="E81" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="F81" s="52"/>
+      <c r="F81" s="56"/>
       <c r="G81" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
+      <c r="I81" s="64"/>
+      <c r="J81" s="64"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
@@ -3453,36 +3363,36 @@
       <c r="B82" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C82" s="52" t="s">
+      <c r="C82" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52" t="s">
+      <c r="D82" s="56"/>
+      <c r="E82" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="F82" s="52"/>
+      <c r="F82" s="56"/>
       <c r="G82" s="11" t="s">
         <v>224</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
+      <c r="I82" s="64"/>
+      <c r="J82" s="64"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83" s="54" t="s">
+      <c r="A83" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="B83" s="55"/>
-      <c r="C83" s="55"/>
-      <c r="D83" s="55"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="55"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="55"/>
-      <c r="I83" s="55"/>
-      <c r="J83" s="55"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="66"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="66"/>
+      <c r="H83" s="66"/>
+      <c r="I83" s="66"/>
+      <c r="J83" s="66"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
@@ -3491,24 +3401,24 @@
       <c r="B84" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="52" t="s">
+      <c r="C84" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52" t="s">
+      <c r="D84" s="56"/>
+      <c r="E84" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="F84" s="52"/>
+      <c r="F84" s="56"/>
       <c r="G84" s="11" t="s">
         <v>228</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="I84" s="49">
+      <c r="I84" s="53">
         <v>4</v>
       </c>
-      <c r="J84" s="49"/>
+      <c r="J84" s="53"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
@@ -3517,22 +3427,22 @@
       <c r="B85" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C85" s="52" t="s">
+      <c r="C85" s="56" t="s">
         <v>230</v>
       </c>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52" t="s">
+      <c r="D85" s="56"/>
+      <c r="E85" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="F85" s="52"/>
+      <c r="F85" s="56"/>
       <c r="G85" s="11" t="s">
         <v>232</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="I85" s="49"/>
-      <c r="J85" s="49"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
@@ -3541,24 +3451,24 @@
       <c r="B86" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="52" t="s">
+      <c r="C86" s="56" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52" t="s">
+      <c r="D86" s="56"/>
+      <c r="E86" s="56" t="s">
         <v>235</v>
       </c>
-      <c r="F86" s="52"/>
+      <c r="F86" s="56"/>
       <c r="G86" s="11" t="s">
         <v>236</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I86" s="53" t="s">
+      <c r="I86" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="J86" s="53"/>
+      <c r="J86" s="64"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
@@ -3567,22 +3477,22 @@
       <c r="B87" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C87" s="52" t="s">
+      <c r="C87" s="56" t="s">
         <v>238</v>
       </c>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52" t="s">
+      <c r="D87" s="56"/>
+      <c r="E87" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="F87" s="52"/>
+      <c r="F87" s="56"/>
       <c r="G87" s="11" t="s">
         <v>240</v>
       </c>
       <c r="H87" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="I87" s="53"/>
-      <c r="J87" s="53"/>
+      <c r="I87" s="64"/>
+      <c r="J87" s="64"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
@@ -3591,22 +3501,22 @@
       <c r="B88" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C88" s="52" t="s">
+      <c r="C88" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52" t="s">
+      <c r="D88" s="56"/>
+      <c r="E88" s="56" t="s">
         <v>243</v>
       </c>
-      <c r="F88" s="52"/>
+      <c r="F88" s="56"/>
       <c r="G88" s="11" t="s">
         <v>244</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="I88" s="53"/>
-      <c r="J88" s="53"/>
+      <c r="I88" s="64"/>
+      <c r="J88" s="64"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
@@ -3615,22 +3525,22 @@
       <c r="B89" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C89" s="52" t="s">
+      <c r="C89" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="D89" s="52"/>
-      <c r="E89" s="52" t="s">
+      <c r="D89" s="56"/>
+      <c r="E89" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="F89" s="52"/>
+      <c r="F89" s="56"/>
       <c r="G89" s="11" t="s">
         <v>248</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
+      <c r="I89" s="64"/>
+      <c r="J89" s="64"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
@@ -3639,22 +3549,22 @@
       <c r="B90" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C90" s="52" t="s">
+      <c r="C90" s="56" t="s">
         <v>250</v>
       </c>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52" t="s">
+      <c r="D90" s="56"/>
+      <c r="E90" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="F90" s="52"/>
+      <c r="F90" s="56"/>
       <c r="G90" s="11" t="s">
         <v>252</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
+      <c r="I90" s="64"/>
+      <c r="J90" s="64"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
@@ -3663,22 +3573,22 @@
       <c r="B91" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C91" s="52" t="s">
+      <c r="C91" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="D91" s="52"/>
-      <c r="E91" s="52" t="s">
+      <c r="D91" s="56"/>
+      <c r="E91" s="56" t="s">
         <v>255</v>
       </c>
-      <c r="F91" s="52"/>
+      <c r="F91" s="56"/>
       <c r="G91" s="11" t="s">
         <v>256</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="I91" s="53"/>
-      <c r="J91" s="53"/>
+      <c r="I91" s="64"/>
+      <c r="J91" s="64"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
@@ -3687,22 +3597,22 @@
       <c r="B92" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C92" s="52" t="s">
+      <c r="C92" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="D92" s="52"/>
-      <c r="E92" s="52" t="s">
+      <c r="D92" s="56"/>
+      <c r="E92" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="F92" s="52"/>
+      <c r="F92" s="56"/>
       <c r="G92" s="11" t="s">
         <v>260</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="I92" s="53"/>
-      <c r="J92" s="53"/>
+      <c r="I92" s="64"/>
+      <c r="J92" s="64"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
@@ -3711,22 +3621,22 @@
       <c r="B93" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C93" s="52" t="s">
+      <c r="C93" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52" t="s">
+      <c r="D93" s="56"/>
+      <c r="E93" s="56" t="s">
         <v>263</v>
       </c>
-      <c r="F93" s="52"/>
+      <c r="F93" s="56"/>
       <c r="G93" s="11" t="s">
         <v>264</v>
       </c>
       <c r="H93" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="I93" s="53"/>
-      <c r="J93" s="53"/>
+      <c r="I93" s="64"/>
+      <c r="J93" s="64"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
@@ -3735,22 +3645,22 @@
       <c r="B94" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C94" s="52" t="s">
+      <c r="C94" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52" t="s">
+      <c r="D94" s="56"/>
+      <c r="E94" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="F94" s="52"/>
+      <c r="F94" s="56"/>
       <c r="G94" s="11" t="s">
         <v>268</v>
       </c>
       <c r="H94" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="I94" s="53"/>
-      <c r="J94" s="53"/>
+      <c r="I94" s="64"/>
+      <c r="J94" s="64"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
@@ -3758,47 +3668,47 @@
       </c>
     </row>
     <row r="111" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="51" t="s">
+      <c r="A111" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="B111" s="51" t="s">
+      <c r="B111" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="C111" s="51"/>
-      <c r="D111" s="50" t="s">
+      <c r="C111" s="57"/>
+      <c r="D111" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E111" s="50"/>
-      <c r="F111" s="50" t="s">
+      <c r="E111" s="46"/>
+      <c r="F111" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="G111" s="50"/>
-      <c r="H111" s="51" t="s">
+      <c r="G111" s="46"/>
+      <c r="H111" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="I111" s="51"/>
-      <c r="J111" s="51"/>
+      <c r="I111" s="57"/>
+      <c r="J111" s="57"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A112" s="51"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="50"/>
-      <c r="E112" s="50"/>
-      <c r="F112" s="50"/>
-      <c r="G112" s="50"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
-      <c r="J112" s="51"/>
+      <c r="A112" s="57"/>
+      <c r="B112" s="57"/>
+      <c r="C112" s="57"/>
+      <c r="D112" s="46"/>
+      <c r="E112" s="46"/>
+      <c r="F112" s="46"/>
+      <c r="G112" s="46"/>
+      <c r="H112" s="57"/>
+      <c r="I112" s="57"/>
+      <c r="J112" s="57"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A113" s="51"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="50"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="50"/>
-      <c r="G113" s="50"/>
+      <c r="A113" s="57"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="46"/>
+      <c r="F113" s="46"/>
+      <c r="G113" s="46"/>
       <c r="H113" s="13" t="s">
         <v>81</v>
       </c>
@@ -3808,87 +3718,87 @@
       <c r="J113" s="61"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="49">
+      <c r="A114" s="53">
         <v>1</v>
       </c>
       <c r="B114" s="14">
         <v>5</v>
       </c>
-      <c r="C114" s="49" t="s">
+      <c r="C114" s="53" t="s">
         <v>65</v>
       </c>
       <c r="D114" s="16">
         <v>2.5</v>
       </c>
-      <c r="E114" s="49" t="s">
+      <c r="E114" s="53" t="s">
         <v>66</v>
       </c>
       <c r="F114" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="G114" s="49" t="s">
+      <c r="G114" s="53" t="s">
         <v>65</v>
       </c>
       <c r="H114" s="41" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="I114" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J114" s="49" t="s">
+      <c r="J114" s="53" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A115" s="49"/>
+      <c r="A115" s="53"/>
       <c r="B115" s="14">
         <v>100</v>
       </c>
-      <c r="C115" s="49"/>
+      <c r="C115" s="53"/>
       <c r="D115" s="16">
         <v>50</v>
       </c>
-      <c r="E115" s="49"/>
+      <c r="E115" s="53"/>
       <c r="F115" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="G115" s="49"/>
+      <c r="G115" s="53"/>
       <c r="H115" s="41" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="I115" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="J115" s="49"/>
+      <c r="J115" s="53"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="49"/>
+      <c r="A116" s="53"/>
       <c r="B116" s="14">
         <v>500</v>
       </c>
-      <c r="C116" s="49"/>
+      <c r="C116" s="53"/>
       <c r="D116" s="16">
         <v>250</v>
       </c>
-      <c r="E116" s="49"/>
+      <c r="E116" s="53"/>
       <c r="F116" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="G116" s="49"/>
+      <c r="G116" s="53"/>
       <c r="H116" s="41" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="I116" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J116" s="49"/>
+      <c r="J116" s="53"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A117" s="49"/>
+      <c r="A117" s="53"/>
       <c r="B117" s="14">
         <v>1</v>
       </c>
-      <c r="C117" s="49" t="s">
+      <c r="C117" s="53" t="s">
         <v>71</v>
       </c>
       <c r="D117" s="16">
@@ -3900,25 +3810,25 @@
       <c r="F117" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="G117" s="49" t="s">
+      <c r="G117" s="53" t="s">
         <v>77</v>
       </c>
       <c r="H117" s="41" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="I117" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="J117" s="49" t="s">
+      <c r="J117" s="53" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A118" s="49"/>
+      <c r="A118" s="53"/>
       <c r="B118" s="14">
         <v>5</v>
       </c>
-      <c r="C118" s="49"/>
+      <c r="C118" s="53"/>
       <c r="D118" s="16">
         <v>2.5</v>
       </c>
@@ -3928,761 +3838,467 @@
       <c r="F118" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="G118" s="49"/>
+      <c r="G118" s="53"/>
       <c r="H118" s="41" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="I118" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="J118" s="49"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A119" s="49">
-        <v>2</v>
-      </c>
-      <c r="B119" s="14">
-        <v>5</v>
-      </c>
-      <c r="C119" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D119" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E119" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F119" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="G119" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="H119" s="41" t="s">
+      <c r="J118" s="53"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+    </row>
+    <row r="121" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="B121" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="C121" s="51"/>
+      <c r="D121" s="51"/>
+      <c r="E121" s="52"/>
+      <c r="F121" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="G121" s="38"/>
+      <c r="H121" s="38"/>
+      <c r="I121" s="38"/>
+      <c r="J121" s="38"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A122" s="49"/>
+      <c r="B122" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="D122" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="F122" s="49"/>
+      <c r="G122" s="38"/>
+      <c r="H122" s="38"/>
+      <c r="I122" s="38"/>
+      <c r="J122" s="38"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B123" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D123" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E123" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="F123" s="53" t="s">
+        <v>291</v>
+      </c>
+      <c r="G123" s="38"/>
+      <c r="H123" s="38"/>
+      <c r="I123" s="38"/>
+      <c r="J123" s="38"/>
+    </row>
+    <row r="124" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B124" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C124" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="D124" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E124" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="I119" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="J119" s="49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A120" s="49"/>
-      <c r="B120" s="14">
-        <v>100</v>
-      </c>
-      <c r="C120" s="49"/>
-      <c r="D120" s="16">
+      <c r="F124" s="53"/>
+      <c r="G124" s="38"/>
+      <c r="H124" s="38"/>
+      <c r="I124" s="38"/>
+      <c r="J124" s="38"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B125" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C125" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="D125" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="E125" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="F125" s="53"/>
+      <c r="G125" s="38"/>
+      <c r="H125" s="38"/>
+      <c r="I125" s="38"/>
+      <c r="J125" s="38"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="C126" s="40" t="s">
+        <v>301</v>
+      </c>
+      <c r="D126" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="E126" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="F126" s="53"/>
+      <c r="G126" s="38"/>
+      <c r="H126" s="38"/>
+      <c r="I126" s="38"/>
+      <c r="J126" s="38"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="E120" s="49"/>
-      <c r="F120" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="G120" s="49"/>
-      <c r="H120" s="41" t="s">
-        <v>296</v>
-      </c>
-      <c r="I120" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J120" s="49"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A121" s="49"/>
-      <c r="B121" s="14">
-        <v>500</v>
-      </c>
-      <c r="C121" s="49"/>
-      <c r="D121" s="16">
-        <v>250</v>
-      </c>
-      <c r="E121" s="49"/>
-      <c r="F121" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="G121" s="49"/>
-      <c r="H121" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="I121" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J121" s="49"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A122" s="49"/>
-      <c r="B122" s="14">
-        <v>1</v>
-      </c>
-      <c r="C122" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D122" s="16">
-        <v>500</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F122" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="G122" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H122" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="I122" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J122" s="49" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A123" s="49"/>
-      <c r="B123" s="14">
-        <v>5</v>
-      </c>
-      <c r="C123" s="49"/>
-      <c r="D123" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F123" s="41" t="s">
-        <v>279</v>
-      </c>
-      <c r="G123" s="49"/>
-      <c r="H123" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="I123" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J123" s="49"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A124" s="49">
-        <v>3</v>
-      </c>
-      <c r="B124" s="14">
-        <v>5</v>
-      </c>
-      <c r="C124" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D124" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E124" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F124" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="G124" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="H124" s="41" t="s">
-        <v>300</v>
-      </c>
-      <c r="I124" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="J124" s="49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A125" s="49"/>
-      <c r="B125" s="14">
-        <v>100</v>
-      </c>
-      <c r="C125" s="49"/>
-      <c r="D125" s="16">
-        <v>50</v>
-      </c>
-      <c r="E125" s="49"/>
-      <c r="F125" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="G125" s="49"/>
-      <c r="H125" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="I125" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J125" s="49"/>
-    </row>
-    <row r="126" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A126" s="49"/>
-      <c r="B126" s="14">
-        <v>500</v>
-      </c>
-      <c r="C126" s="49"/>
-      <c r="D126" s="16">
-        <v>250</v>
-      </c>
-      <c r="E126" s="49"/>
-      <c r="F126" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="G126" s="49"/>
-      <c r="H126" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="I126" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J126" s="49"/>
-    </row>
-    <row r="127" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A127" s="49"/>
-      <c r="B127" s="14">
-        <v>1</v>
-      </c>
-      <c r="C127" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D127" s="16">
-        <v>500</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F127" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="G127" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H127" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="I127" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J127" s="49" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A128" s="49"/>
-      <c r="B128" s="14">
-        <v>5</v>
-      </c>
-      <c r="C128" s="49"/>
-      <c r="D128" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E128" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F128" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="G128" s="49"/>
-      <c r="H128" s="41" t="s">
+      <c r="B127" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="I128" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J128" s="49"/>
-    </row>
-    <row r="129" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A129" s="49">
-        <v>4</v>
-      </c>
-      <c r="B129" s="14">
-        <v>5</v>
-      </c>
-      <c r="C129" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D129" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E129" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F129" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="G129" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="H129" s="41" t="s">
+      <c r="C127" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="I129" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="J129" s="49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A130" s="49"/>
-      <c r="B130" s="14">
-        <v>100</v>
-      </c>
-      <c r="C130" s="49"/>
-      <c r="D130" s="16">
-        <v>50</v>
-      </c>
-      <c r="E130" s="49"/>
-      <c r="F130" s="41" t="s">
-        <v>286</v>
-      </c>
-      <c r="G130" s="49"/>
-      <c r="H130" s="41" t="s">
+      <c r="D127" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="I130" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J130" s="49"/>
-    </row>
-    <row r="131" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A131" s="49"/>
-      <c r="B131" s="14">
-        <v>500</v>
-      </c>
-      <c r="C131" s="49"/>
-      <c r="D131" s="16">
-        <v>250</v>
-      </c>
-      <c r="E131" s="49"/>
-      <c r="F131" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="G131" s="49"/>
-      <c r="H131" s="41" t="s">
+      <c r="E127" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="I131" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J131" s="49"/>
-    </row>
-    <row r="132" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A132" s="49"/>
-      <c r="B132" s="14">
-        <v>1</v>
-      </c>
-      <c r="C132" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D132" s="16">
-        <v>500</v>
-      </c>
-      <c r="E132" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F132" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="G132" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H132" s="41" t="s">
+      <c r="F127" s="53"/>
+      <c r="G127" s="38"/>
+      <c r="H127" s="38"/>
+      <c r="I127" s="38"/>
+      <c r="J127" s="38"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" s="40" t="s">
         <v>308</v>
       </c>
-      <c r="I132" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J132" s="49" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A133" s="49"/>
-      <c r="B133" s="14">
-        <v>5</v>
-      </c>
-      <c r="C133" s="49"/>
-      <c r="D133" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E133" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F133" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="G133" s="49"/>
-      <c r="H133" s="41" t="s">
+      <c r="C128" s="40" t="s">
         <v>309</v>
       </c>
-      <c r="I133" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J133" s="49"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="3"/>
-      <c r="J135" s="3"/>
-    </row>
-    <row r="136" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="65" t="s">
+      <c r="D128" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="E128" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="B136" s="67" t="s">
+      <c r="F128" s="53"/>
+      <c r="G128" s="38"/>
+      <c r="H128" s="38"/>
+      <c r="I128" s="38"/>
+      <c r="J128" s="38"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B129" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="C136" s="68"/>
-      <c r="D136" s="68"/>
-      <c r="E136" s="69"/>
-      <c r="F136" s="65" t="s">
+      <c r="C129" s="40" t="s">
         <v>313</v>
       </c>
-      <c r="G136" s="38"/>
-      <c r="H136" s="38"/>
-      <c r="I136" s="38"/>
-      <c r="J136" s="38"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A137" s="66"/>
-      <c r="B137" s="37" t="s">
+      <c r="D129" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="C137" s="37" t="s">
+      <c r="E129" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="D137" s="37" t="s">
+      <c r="F129" s="53"/>
+      <c r="G129" s="38"/>
+      <c r="H129" s="38"/>
+      <c r="I129" s="38"/>
+      <c r="J129" s="38"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B130" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="E137" s="37" t="s">
+      <c r="C130" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="F137" s="66"/>
-      <c r="G137" s="38"/>
-      <c r="H137" s="38"/>
-      <c r="I137" s="38"/>
-      <c r="J137" s="38"/>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B138" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="C138" s="40" t="s">
+      <c r="D130" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="D138" s="40" t="s">
+      <c r="E130" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="E138" s="40" t="s">
+      <c r="F130" s="53"/>
+      <c r="G130" s="38"/>
+      <c r="H130" s="38"/>
+      <c r="I130" s="38"/>
+      <c r="J130" s="38"/>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B131" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="F138" s="49" t="s">
+      <c r="C131" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="G138" s="38"/>
-      <c r="H138" s="38"/>
-      <c r="I138" s="38"/>
-      <c r="J138" s="38"/>
-    </row>
-    <row r="139" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B139" s="40" t="s">
+      <c r="D131" s="40" t="s">
         <v>322</v>
       </c>
-      <c r="C139" s="40" t="s">
+      <c r="E131" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="D139" s="40" t="s">
+      <c r="F131" s="53"/>
+      <c r="G131" s="38"/>
+      <c r="H131" s="38"/>
+      <c r="I131" s="38"/>
+      <c r="J131" s="38"/>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="E139" s="40" t="s">
+      <c r="C132" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="F139" s="49"/>
-      <c r="G139" s="38"/>
-      <c r="H139" s="38"/>
-      <c r="I139" s="38"/>
-      <c r="J139" s="38"/>
-    </row>
-    <row r="140" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B140" s="40" t="s">
+      <c r="D132" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="C140" s="40" t="s">
+      <c r="E132" s="40" t="s">
         <v>327</v>
       </c>
-      <c r="D140" s="40" t="s">
-        <v>328</v>
-      </c>
-      <c r="E140" s="40" t="s">
-        <v>329</v>
-      </c>
-      <c r="F140" s="49"/>
-      <c r="G140" s="38"/>
-      <c r="H140" s="38"/>
-      <c r="I140" s="38"/>
-      <c r="J140" s="38"/>
-    </row>
-    <row r="141" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B141" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="C141" s="40" t="s">
-        <v>331</v>
-      </c>
-      <c r="D141" s="40" t="s">
-        <v>332</v>
-      </c>
-      <c r="E141" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="F141" s="49"/>
-      <c r="G141" s="38"/>
-      <c r="H141" s="38"/>
-      <c r="I141" s="38"/>
-      <c r="J141" s="38"/>
-    </row>
-    <row r="142" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B142" s="40" t="s">
-        <v>334</v>
-      </c>
-      <c r="C142" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="D142" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="E142" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="F142" s="49"/>
-      <c r="G142" s="38"/>
-      <c r="H142" s="38"/>
-      <c r="I142" s="38"/>
-      <c r="J142" s="38"/>
-    </row>
-    <row r="143" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B143" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="C143" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="D143" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="E143" s="40" t="s">
-        <v>341</v>
-      </c>
-      <c r="F143" s="49"/>
-      <c r="G143" s="38"/>
-      <c r="H143" s="38"/>
-      <c r="I143" s="38"/>
-      <c r="J143" s="38"/>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B144" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="C144" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="D144" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="E144" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="F144" s="49"/>
-      <c r="G144" s="38"/>
-      <c r="H144" s="38"/>
-      <c r="I144" s="38"/>
-      <c r="J144" s="38"/>
-    </row>
-    <row r="145" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B145" s="40" t="s">
-        <v>346</v>
-      </c>
-      <c r="C145" s="40" t="s">
-        <v>347</v>
-      </c>
-      <c r="D145" s="40" t="s">
-        <v>348</v>
-      </c>
-      <c r="E145" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="F145" s="49"/>
-      <c r="G145" s="38"/>
-      <c r="H145" s="38"/>
-      <c r="I145" s="38"/>
-      <c r="J145" s="38"/>
-    </row>
-    <row r="146" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B146" s="40" t="s">
-        <v>350</v>
-      </c>
-      <c r="C146" s="40" t="s">
-        <v>351</v>
-      </c>
-      <c r="D146" s="40" t="s">
-        <v>352</v>
-      </c>
-      <c r="E146" s="40" t="s">
-        <v>353</v>
-      </c>
-      <c r="F146" s="49"/>
-      <c r="G146" s="38"/>
-      <c r="H146" s="38"/>
-      <c r="I146" s="38"/>
-      <c r="J146" s="38"/>
-    </row>
-    <row r="147" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B147" s="40" t="s">
-        <v>354</v>
-      </c>
-      <c r="C147" s="40" t="s">
-        <v>355</v>
-      </c>
-      <c r="D147" s="40" t="s">
-        <v>356</v>
-      </c>
-      <c r="E147" s="40" t="s">
-        <v>357</v>
-      </c>
-      <c r="F147" s="49"/>
-      <c r="G147" s="38"/>
-      <c r="H147" s="38"/>
-      <c r="I147" s="38"/>
-      <c r="J147" s="38"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A148" s="38"/>
-      <c r="B148" s="38"/>
-      <c r="C148" s="38"/>
-      <c r="D148" s="38"/>
-      <c r="E148" s="38"/>
-      <c r="F148" s="38"/>
-      <c r="G148" s="38"/>
-      <c r="H148" s="38"/>
-      <c r="I148" s="38"/>
-      <c r="J148" s="38"/>
-    </row>
-    <row r="150" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A150" s="62" t="s">
+      <c r="F132" s="53"/>
+      <c r="G132" s="38"/>
+      <c r="H132" s="38"/>
+      <c r="I132" s="38"/>
+      <c r="J132" s="38"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A133" s="38"/>
+      <c r="B133" s="38"/>
+      <c r="C133" s="38"/>
+      <c r="D133" s="38"/>
+      <c r="E133" s="38"/>
+      <c r="F133" s="38"/>
+      <c r="G133" s="38"/>
+      <c r="H133" s="38"/>
+      <c r="I133" s="38"/>
+      <c r="J133" s="38"/>
+    </row>
+    <row r="135" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A135" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="B150" s="62"/>
-      <c r="C150" s="33"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="34"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-    </row>
-    <row r="151" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A151" s="62" t="s">
+      <c r="B135" s="44"/>
+      <c r="C135" s="33"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+      <c r="F135" s="34"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A136" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="B151" s="62"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="8" t="s">
+      <c r="B136" s="44"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E151" s="70" t="s">
+      <c r="E136" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="F151" s="71"/>
-      <c r="G151" s="9" t="s">
+      <c r="F136" s="55"/>
+      <c r="G136" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H151" s="10"/>
-    </row>
-    <row r="152" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A152" s="62" t="s">
+      <c r="H136" s="10"/>
+    </row>
+    <row r="137" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A137" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="B152" s="62"/>
-      <c r="C152" s="63" t="s">
+      <c r="B137" s="44"/>
+      <c r="C137" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D152" s="63"/>
-      <c r="E152" s="1"/>
-      <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
-      <c r="H152" s="1"/>
+      <c r="D137" s="45"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="190">
-    <mergeCell ref="A152:B152"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="G35:H38"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:E136"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="F138:F147"/>
-    <mergeCell ref="A150:B150"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="E151:F151"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="J129:J131"/>
-    <mergeCell ref="J132:J133"/>
-    <mergeCell ref="E35:F39"/>
-    <mergeCell ref="I35:J39"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C54:D58"/>
-    <mergeCell ref="E54:F58"/>
-    <mergeCell ref="J114:J116"/>
+  <mergeCells count="166">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="I72:J73"/>
+    <mergeCell ref="A18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G54:H57"/>
+    <mergeCell ref="I54:J58"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I60:J61"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="I62:J70"/>
+    <mergeCell ref="I74:J82"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="J117:J118"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="I86:J94"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="I84:J85"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="I43:J51"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B111:C113"/>
     <mergeCell ref="D111:E113"/>
@@ -4707,148 +4323,28 @@
     <mergeCell ref="C35:D39"/>
     <mergeCell ref="H111:J112"/>
     <mergeCell ref="I113:J113"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="I43:J51"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="A83:J83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="I84:J85"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="J117:J118"/>
-    <mergeCell ref="J119:J121"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="I86:J94"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="J122:J123"/>
-    <mergeCell ref="J124:J126"/>
-    <mergeCell ref="J127:J128"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="I72:J73"/>
-    <mergeCell ref="A18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G54:H57"/>
-    <mergeCell ref="I54:J58"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="I60:J61"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="I62:J70"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="I74:J82"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="A129:A133"/>
-    <mergeCell ref="C129:C131"/>
-    <mergeCell ref="E129:E131"/>
-    <mergeCell ref="G129:G131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="E119:E121"/>
-    <mergeCell ref="G119:G121"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="A124:A128"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="E124:E126"/>
-    <mergeCell ref="G124:G126"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="G35:H38"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="F123:F132"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E35:F39"/>
+    <mergeCell ref="I35:J39"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C54:D58"/>
+    <mergeCell ref="E54:F58"/>
+    <mergeCell ref="J114:J116"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.78125" header="0.51181102362204722" footer="0.51181102362204722"/>
